--- a/model_maker_web_v2/results/Kstar/Kstar_stage2.xlsx
+++ b/model_maker_web_v2/results/Kstar/Kstar_stage2.xlsx
@@ -516,7 +516,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Kstar</t>
         </is>
       </c>
     </row>
@@ -12110,7 +12110,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Kstar</t>
         </is>
       </c>
     </row>
